--- a/config/world_boss/role_rank_award.xlsx
+++ b/config/world_boss/role_rank_award.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="role_rank_award" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="role_rank_award" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1098,9 +1098,7 @@
           <t>默认值</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>{}</t>
@@ -1202,7 +1200,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1249,7 +1247,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1296,7 +1294,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1343,7 +1341,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1390,7 +1388,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1437,7 +1435,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1484,7 +1482,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1531,7 +1529,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1578,7 +1576,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1625,7 +1623,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1672,7 +1670,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1719,7 +1717,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1739,15 +1737,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1777,7 +1768,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1824,7 +1815,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1871,7 +1862,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1918,7 +1909,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1965,7 +1956,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2012,7 +2003,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2059,7 +2050,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2106,7 +2097,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2153,7 +2144,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2200,7 +2191,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2247,7 +2238,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2294,7 +2285,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2314,15 +2305,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2352,7 +2336,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2399,7 +2383,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2446,7 +2430,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2493,7 +2477,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2540,7 +2524,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2587,7 +2571,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2634,7 +2618,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2681,7 +2665,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2728,7 +2712,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2775,7 +2759,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2822,7 +2806,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2869,7 +2853,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2889,15 +2873,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2927,7 +2904,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2974,7 +2951,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3021,7 +2998,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3068,7 +3045,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3115,7 +3092,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3162,7 +3139,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3209,7 +3186,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3256,7 +3233,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3303,7 +3280,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3350,7 +3327,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3397,7 +3374,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3444,7 +3421,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3464,15 +3441,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3502,7 +3472,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3549,7 +3519,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3596,7 +3566,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3643,7 +3613,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3690,7 +3660,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3737,7 +3707,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3784,7 +3754,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3831,7 +3801,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3878,7 +3848,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3925,7 +3895,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3972,7 +3942,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4019,7 +3989,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4039,15 +4009,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4077,7 +4040,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4124,7 +4087,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4171,7 +4134,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4218,7 +4181,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4265,7 +4228,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4312,7 +4275,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4359,7 +4322,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4406,7 +4369,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4453,7 +4416,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4500,7 +4463,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4547,7 +4510,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4594,7 +4557,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4614,15 +4577,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4652,7 +4608,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4699,7 +4655,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4746,7 +4702,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4793,7 +4749,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4840,7 +4796,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4887,7 +4843,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4934,7 +4890,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4981,7 +4937,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5028,7 +4984,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5075,7 +5031,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5122,7 +5078,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5169,7 +5125,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5189,15 +5145,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5227,7 +5176,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5274,7 +5223,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5321,7 +5270,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5368,7 +5317,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5415,7 +5364,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5462,7 +5411,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5509,7 +5458,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5556,7 +5505,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5603,7 +5552,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5650,7 +5599,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5697,7 +5646,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -5744,7 +5693,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -5764,15 +5713,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5802,7 +5744,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -5849,7 +5791,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -5896,7 +5838,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -5943,7 +5885,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -5990,7 +5932,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6037,7 +5979,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6084,7 +6026,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6131,7 +6073,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6178,7 +6120,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6225,7 +6167,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6272,7 +6214,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6319,7 +6261,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6339,15 +6281,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6377,7 +6312,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -6424,7 +6359,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6471,7 +6406,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -6518,7 +6453,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6565,7 +6500,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -6612,7 +6547,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -6659,7 +6594,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -6706,7 +6641,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -6753,7 +6688,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -6800,7 +6735,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -6847,7 +6782,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -6894,7 +6829,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -6914,15 +6849,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6952,7 +6880,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -6999,7 +6927,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7046,7 +6974,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -7093,7 +7021,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -7140,7 +7068,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -7187,7 +7115,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -7234,7 +7162,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -7281,7 +7209,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -7328,7 +7256,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -7375,7 +7303,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -7422,7 +7350,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -7469,7 +7397,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -7489,15 +7417,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
-      <c r="B146" t="inlineStr"/>
       <c r="C146" s="2" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7527,7 +7448,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -7574,7 +7495,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -7621,7 +7542,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -7668,7 +7589,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -7715,7 +7636,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -7762,7 +7683,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -7809,7 +7730,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -7856,7 +7777,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -7903,7 +7824,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -7950,7 +7871,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -7997,7 +7918,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -8044,7 +7965,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>世界ボス報酬</t>
+          <t>世界boss报酬</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
